--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92576E97-59EC-4829-97E1-8C2CF98A931E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B834CEC6-B0C1-4743-88D0-F61616638EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -197,6 +197,15 @@
   </si>
   <si>
     <t>Boring</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>having a good vibe</t>
   </si>
 </sst>
 </file>
@@ -1022,26 +1031,50 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B7" s="14">
+        <v>480</v>
+      </c>
+      <c r="C7" s="14">
+        <v>20</v>
+      </c>
+      <c r="D7" s="14">
+        <v>110</v>
+      </c>
+      <c r="E7" s="14">
+        <v>60</v>
+      </c>
+      <c r="F7" s="14">
+        <v>350</v>
+      </c>
+      <c r="G7" s="14">
+        <v>7</v>
+      </c>
+      <c r="H7" s="14">
+        <v>350</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>70</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B834CEC6-B0C1-4743-88D0-F61616638EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39BB95DB-9ACA-409E-84A3-E8FB83B71868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -206,6 +206,15 @@
   </si>
   <si>
     <t>having a good vibe</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>lost my charger</t>
   </si>
 </sst>
 </file>
@@ -1077,26 +1086,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46048</v>
+      </c>
+      <c r="B8" s="14">
+        <v>400</v>
+      </c>
+      <c r="C8" s="14">
+        <v>20</v>
+      </c>
+      <c r="D8" s="14">
+        <v>120</v>
+      </c>
+      <c r="E8" s="14">
+        <v>45</v>
+      </c>
+      <c r="F8" s="14">
+        <v>300</v>
+      </c>
+      <c r="G8" s="14">
+        <v>6</v>
+      </c>
+      <c r="H8" s="14">
+        <v>370</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1255</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>185</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39BB95DB-9ACA-409E-84A3-E8FB83B71868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B23EDDE-735A-4256-8F2F-385AAF337DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>lost my charger</t>
+  </si>
+  <si>
+    <t>31-09-2026</t>
+  </si>
+  <si>
+    <t>usual</t>
   </si>
 </sst>
 </file>
@@ -1132,26 +1138,50 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="14">
+        <v>450</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>40</v>
+      </c>
+      <c r="F9" s="14">
+        <v>200</v>
+      </c>
+      <c r="G9" s="14">
+        <v>4</v>
+      </c>
+      <c r="H9" s="14">
+        <v>500</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B23EDDE-735A-4256-8F2F-385AAF337DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8456DA8C-72A2-4D2A-9D17-3CA563C82A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -217,10 +217,10 @@
     <t>lost my charger</t>
   </si>
   <si>
-    <t>31-09-2026</t>
+    <t>usual</t>
   </si>
   <si>
-    <t>usual</t>
+    <t>good day</t>
   </si>
 </sst>
 </file>
@@ -1138,8 +1138,8 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
-        <v>63</v>
+      <c r="A9" s="13">
+        <v>46265</v>
       </c>
       <c r="B9" s="14">
         <v>450</v>
@@ -1180,30 +1180,54 @@
         <v>48</v>
       </c>
       <c r="N9" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B10" s="14">
+        <v>360</v>
+      </c>
+      <c r="C10" s="14">
+        <v>25</v>
+      </c>
+      <c r="D10" s="14">
+        <v>160</v>
+      </c>
+      <c r="E10" s="14">
+        <v>60</v>
+      </c>
+      <c r="F10" s="14">
+        <v>300</v>
+      </c>
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
+        <v>380</v>
+      </c>
+      <c r="I10" s="15">
+        <f t="shared" si="0"/>
+        <v>1285</v>
+      </c>
+      <c r="J10" s="15">
+        <f t="shared" si="1"/>
+        <v>155</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N10" s="17" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8456DA8C-72A2-4D2A-9D17-3CA563C82A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CA344D-0965-491B-8DB5-A68AB32386B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,12 @@
   </si>
   <si>
     <t>good day</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Daily vibe</t>
   </si>
 </sst>
 </file>
@@ -1230,26 +1236,50 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
+      <c r="C11" s="14">
+        <v>20</v>
+      </c>
+      <c r="D11" s="14">
+        <v>90</v>
+      </c>
+      <c r="E11" s="14">
+        <v>50</v>
+      </c>
+      <c r="F11" s="14">
+        <v>350</v>
+      </c>
+      <c r="G11" s="14">
+        <v>7</v>
+      </c>
+      <c r="H11" s="14">
+        <v>350</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/12621277.xlsx
+++ b/12621277.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aman1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CA344D-0965-491B-8DB5-A68AB32386B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663D9A88-E057-47E2-B19A-7152E42E5FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>Daily vibe</t>
+  </si>
+  <si>
+    <t>Daily routine</t>
   </si>
 </sst>
 </file>
@@ -1282,26 +1285,50 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B12" s="14">
+        <v>380</v>
+      </c>
+      <c r="C12" s="14">
+        <v>24</v>
+      </c>
+      <c r="D12" s="14">
+        <v>160</v>
+      </c>
+      <c r="E12" s="14">
+        <v>40</v>
+      </c>
+      <c r="F12" s="14">
+        <v>350</v>
+      </c>
+      <c r="G12" s="14">
+        <v>7</v>
+      </c>
+      <c r="H12" s="14">
+        <v>390</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1344</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>96</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
